--- a/product family/MX150/MX150 2X10 RCPT (33472)/BOM.xlsx
+++ b/product family/MX150/MX150 2X10 RCPT (33472)/BOM.xlsx
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
         <v>334722001</v>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
         <v>334722001</v>
@@ -623,10 +623,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
         <v>334722001</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
         <v>334722001</v>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
         <v>334722001</v>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>334722002</v>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
         <v>334722002</v>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
         <v>334722002</v>
@@ -823,10 +823,10 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
         <v>334722002</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
         <v>334722002</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H13" t="n">
         <v>334722002</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
         <v>334722006</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
         <v>334722006</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
         <v>334722006</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
         <v>334722006</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H19" t="n">
         <v>334722006</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>334722007</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
         <v>334722007</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H22" t="n">
         <v>334722007</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H23" t="n">
         <v>334722007</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
         <v>334722007</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
         <v>334722007</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
         <v>334722501</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H27" t="n">
         <v>334722501</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H28" t="n">
         <v>334722501</v>
@@ -1455,10 +1455,10 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H29" t="n">
         <v>334722501</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
         <v>334722501</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H31" t="n">
         <v>334722501</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
         <v>334722502</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H33" t="n">
         <v>334722502</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H34" t="n">
         <v>334722502</v>
@@ -1655,10 +1655,10 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H35" t="n">
         <v>334722502</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H36" t="n">
         <v>334722502</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H37" t="n">
         <v>334722502</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H38" t="n">
         <v>334722503</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H39" t="n">
         <v>334722503</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H40" t="n">
         <v>334722503</v>
@@ -1855,10 +1855,10 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H41" t="n">
         <v>334722503</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
         <v>334722503</v>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H43" t="n">
         <v>334722503</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" t="n">
         <v>334722504</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H45" t="n">
         <v>334722504</v>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H46" t="n">
         <v>334722504</v>
@@ -2055,10 +2055,10 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H47" t="n">
         <v>334722504</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H48" t="n">
         <v>334722504</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H49" t="n">
         <v>334722504</v>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H50" t="n">
         <v>334722506</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H51" t="n">
         <v>334722506</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H52" t="n">
         <v>334722506</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H53" t="n">
         <v>334722506</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
         <v>334722506</v>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G55" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H55" t="n">
         <v>334722506</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H56" t="n">
         <v>334722507</v>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H57" t="n">
         <v>334722507</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H58" t="n">
         <v>334722507</v>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H59" t="n">
         <v>334722507</v>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H60" t="n">
         <v>334722507</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H61" t="n">
         <v>334722507</v>
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H62" t="n">
         <v>334722508</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H63" t="n">
         <v>334722508</v>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H64" t="n">
         <v>334722508</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G65" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H65" t="n">
         <v>334722508</v>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H66" t="n">
         <v>334722508</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H67" t="n">
         <v>334722508</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H68" t="n">
         <v>334722509</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H69" t="n">
         <v>334722509</v>
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H70" t="n">
         <v>334722509</v>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H71" t="n">
         <v>334722509</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H72" t="n">
         <v>334722509</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H73" t="n">
         <v>334722509</v>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H74" t="n">
         <v>334722638</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H75" t="n">
         <v>334722638</v>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H76" t="n">
         <v>334722638</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H77" t="n">
         <v>334722638</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G78" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H78" t="n">
         <v>334722638</v>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G79" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H79" t="n">
         <v>334722638</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H80" t="n">
         <v>334722640</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H81" t="n">
         <v>334722640</v>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H82" t="n">
         <v>334722640</v>
@@ -3335,10 +3335,10 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H83" t="n">
         <v>334722640</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G84" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H84" t="n">
         <v>334722640</v>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H85" t="n">
         <v>334722640</v>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H86" t="n">
         <v>334722643</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H87" t="n">
         <v>334722643</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G88" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H88" t="n">
         <v>334722643</v>
@@ -3535,10 +3535,10 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H89" t="n">
         <v>334722643</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H90" t="n">
         <v>334722643</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H91" t="n">
         <v>334722643</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H92" t="n">
         <v>334722645</v>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H93" t="n">
         <v>334722645</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H94" t="n">
         <v>334722645</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G95" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H95" t="n">
         <v>334722645</v>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G96" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H96" t="n">
         <v>334722645</v>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H97" t="n">
         <v>334722645</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H99" t="n">
         <v>334722001</v>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G100" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H100" t="n">
         <v>334722001</v>
@@ -3951,10 +3951,10 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G101" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H101" t="n">
         <v>334722001</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G102" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H102" t="n">
         <v>334722001</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H103" t="n">
         <v>334722001</v>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" t="n">
         <v>334722002</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H105" t="n">
         <v>334722002</v>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H106" t="n">
         <v>334722002</v>
@@ -4151,10 +4151,10 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H107" t="n">
         <v>334722002</v>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H108" t="n">
         <v>334722002</v>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G109" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H109" t="n">
         <v>334722002</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H111" t="n">
         <v>334722006</v>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H112" t="n">
         <v>334722006</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G113" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H113" t="n">
         <v>334722006</v>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G114" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H114" t="n">
         <v>334722006</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G115" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H115" t="n">
         <v>334722006</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
         <v>334722007</v>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H117" t="n">
         <v>334722007</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G118" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H118" t="n">
         <v>334722007</v>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G119" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H119" t="n">
         <v>334722007</v>
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G120" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H120" t="n">
         <v>334722007</v>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G121" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H121" t="n">
         <v>334722007</v>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H122" t="n">
         <v>334722501</v>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H123" t="n">
         <v>334722501</v>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H124" t="n">
         <v>334722501</v>
@@ -4783,10 +4783,10 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G125" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H125" t="n">
         <v>334722501</v>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G126" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H126" t="n">
         <v>334722501</v>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G127" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H127" t="n">
         <v>334722501</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H128" t="n">
         <v>334722502</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H129" t="n">
         <v>334722502</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H130" t="n">
         <v>334722502</v>
@@ -4983,10 +4983,10 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G131" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H131" t="n">
         <v>334722502</v>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G132" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H132" t="n">
         <v>334722502</v>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G133" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H133" t="n">
         <v>334722502</v>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H134" t="n">
         <v>334722503</v>
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H135" t="n">
         <v>334722503</v>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G136" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H136" t="n">
         <v>334722503</v>
@@ -5183,10 +5183,10 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G137" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H137" t="n">
         <v>334722503</v>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G138" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H138" t="n">
         <v>334722503</v>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G139" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H139" t="n">
         <v>334722503</v>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H140" t="n">
         <v>334722504</v>
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H141" t="n">
         <v>334722504</v>
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H142" t="n">
         <v>334722504</v>
@@ -5383,10 +5383,10 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G143" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H143" t="n">
         <v>334722504</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G144" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H144" t="n">
         <v>334722504</v>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G145" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H145" t="n">
         <v>334722504</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H146" t="n">
         <v>334722506</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H147" t="n">
         <v>334722506</v>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G148" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H148" t="n">
         <v>334722506</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G149" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H149" t="n">
         <v>334722506</v>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G150" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H150" t="n">
         <v>334722506</v>
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G151" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H151" t="n">
         <v>334722506</v>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H152" t="n">
         <v>334722507</v>
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H153" t="n">
         <v>334722507</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G154" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H154" t="n">
         <v>334722507</v>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G155" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H155" t="n">
         <v>334722507</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G156" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H156" t="n">
         <v>334722507</v>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G157" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H157" t="n">
         <v>334722507</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H158" t="n">
         <v>334722508</v>
@@ -5959,10 +5959,10 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H159" t="n">
         <v>334722508</v>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H160" t="n">
         <v>334722508</v>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G161" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H161" t="n">
         <v>334722508</v>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G162" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H162" t="n">
         <v>334722508</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G163" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H163" t="n">
         <v>334722508</v>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H164" t="n">
         <v>334722509</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G165" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H165" t="n">
         <v>334722509</v>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G166" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H166" t="n">
         <v>334722509</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G167" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H167" t="n">
         <v>334722509</v>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G168" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H168" t="n">
         <v>334722509</v>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G169" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H169" t="n">
         <v>334722509</v>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H170" t="n">
         <v>334722638</v>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G171" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H171" t="n">
         <v>334722638</v>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H172" t="n">
         <v>334722638</v>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G173" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H173" t="n">
         <v>334722638</v>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G174" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H174" t="n">
         <v>334722638</v>
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G175" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H175" t="n">
         <v>334722638</v>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H176" t="n">
         <v>334722640</v>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H177" t="n">
         <v>334722640</v>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G178" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H178" t="n">
         <v>334722640</v>
@@ -6663,10 +6663,10 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G179" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H179" t="n">
         <v>334722640</v>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G180" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H180" t="n">
         <v>334722640</v>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G181" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H181" t="n">
         <v>334722640</v>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H182" t="n">
         <v>334722643</v>
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H183" t="n">
         <v>334722643</v>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H184" t="n">
         <v>334722643</v>
@@ -6863,10 +6863,10 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G185" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H185" t="n">
         <v>334722643</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G186" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H186" t="n">
         <v>334722643</v>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G187" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H187" t="n">
         <v>334722643</v>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H188" t="n">
         <v>334722645</v>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H189" t="n">
         <v>334722645</v>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G190" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H190" t="n">
         <v>334722645</v>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G191" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H191" t="n">
         <v>334722645</v>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G192" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H192" t="n">
         <v>334722645</v>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G193" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H193" t="n">
         <v>334722645</v>
